--- a/data/raw/sniim/sniim_format_test_xlsx.xlsx
+++ b/data/raw/sniim/sniim_format_test_xlsx.xlsx
@@ -431,12 +431,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>columna_a</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>columna_b</t>
         </is>
       </c>
     </row>
